--- a/docs/resources/problems_revise.xlsx
+++ b/docs/resources/problems_revise.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ankit Shivane\Documents\repos\DSA-Skill-builder\docs\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0F02285-5727-47F7-894D-0FB5EF9A27C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364E8E5B-148D-42AC-91A9-4729D8793F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{72B1520C-83A9-4B84-B49F-F5ED5A2D9D4B}"/>
   </bookViews>
@@ -35,15 +35,149 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
+  <si>
+    <t>FirstNonRepeatingChar</t>
+  </si>
+  <si>
+    <t>_3ConseThreeNumbers</t>
+  </si>
+  <si>
+    <t>_10GFGValueEqualToPosition</t>
+  </si>
+  <si>
+    <t>Gfg_max_sum_array</t>
+  </si>
+  <si>
+    <t>_5MinMaxGfg</t>
+  </si>
+  <si>
+    <t>GfgElementsInRange</t>
+  </si>
+  <si>
+    <t>GfgReverseArrayInPlace</t>
+  </si>
+  <si>
+    <t>GFGCheckIfArrayIsSorted</t>
+  </si>
+  <si>
+    <t>LCFindEvenDigitsInNumber</t>
+  </si>
+  <si>
+    <t>InsertInArrayAtGivenPos</t>
+  </si>
+  <si>
+    <t>Gfg_pod_NextGreaterCircularArray</t>
+  </si>
+  <si>
+    <t>GfgArrayIsSubArray</t>
+  </si>
+  <si>
+    <t>RemoveDuplicate</t>
+  </si>
+  <si>
+    <t>RemoveDuplicateFromSortedArray</t>
+  </si>
+  <si>
+    <t>SecondLargestInArr</t>
+  </si>
+  <si>
+    <t>StringArray</t>
+  </si>
+  <si>
+    <t>TwoSumLC</t>
+  </si>
+  <si>
+    <t>UnionOfTwo</t>
+  </si>
+  <si>
+    <t>xor pkg problem</t>
+  </si>
+  <si>
+    <t>hashing</t>
+  </si>
+  <si>
+    <t>math</t>
+  </si>
+  <si>
+    <t>_1GFGLastOne</t>
+  </si>
+  <si>
+    <t>_2GfgConvertStringToLowerCase</t>
+  </si>
+  <si>
+    <t>_3GfgUncommonCharacters</t>
+  </si>
+  <si>
+    <t>_4FirstOccurrence</t>
+  </si>
+  <si>
+    <t>_6GFGMaxGapBetweenTwoSame</t>
+  </si>
+  <si>
+    <t>CompressString</t>
+  </si>
+  <si>
+    <t>CountVowelConsonant</t>
+  </si>
+  <si>
+    <t>FrequenceOfEachCharacter</t>
+  </si>
+  <si>
+    <t>GFGNonRepeatingCharStr</t>
+  </si>
+  <si>
+    <t>NonRepeatedChar</t>
+  </si>
+  <si>
+    <t>OccurrenceOfChar</t>
+  </si>
+  <si>
+    <t>RemoveDupCharFromStr</t>
+  </si>
+  <si>
+    <t>ReverseAString</t>
+  </si>
+  <si>
+    <t>ReverseEachWordInStr</t>
+  </si>
+  <si>
+    <t>ReverseStr</t>
+  </si>
+  <si>
+    <t>ReverseStringGFG</t>
+  </si>
+  <si>
+    <t>ValidAnagram</t>
+  </si>
+  <si>
+    <t>program names</t>
+  </si>
+  <si>
+    <t>̥</t>
+  </si>
+  <si>
+    <t>revise number of times</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FFBCBEC4"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -66,8 +200,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,9 +539,225 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59B091D0-65A5-481B-85EB-2BBE5AABB66D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>